--- a/insumos/02_listado_act/Actividades_CAB-SIPP_12092024.xlsx
+++ b/insumos/02_listado_act/Actividades_CAB-SIPP_12092024.xlsx
@@ -551,7 +551,7 @@
   <dimension ref="A1:A56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
